--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -67,6 +67,7 @@
     <sheet name="2026-09-10" sheetId="58" state="visible" r:id="rId58"/>
     <sheet name="2026-09-11" sheetId="59" state="visible" r:id="rId59"/>
     <sheet name="2026-09-12" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="2026-09-13" sheetId="61" state="visible" r:id="rId61"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -50595,6 +50596,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-13 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>6672</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2975</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+593</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>17504</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+3696</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ZÎ£ WHITÎ£BÎ£ARD</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>AangEX2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>5520</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>8409</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+2575</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>el MeiMei</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2072</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>C.L.A.Z</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>6474</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>34550</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>21360</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+1470</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>32101</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | $ignature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>5074</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1441</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>16002</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>7162</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>44877</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+6792</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>34923</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3238</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>10283</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1084</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -50620,7 +50620,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-13 13:01:00</t>
+          <t>Timestamp: 2026-09-13 13:31:00</t>
         </is>
       </c>
     </row>
@@ -51368,11 +51368,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>44877</v>
+        <v>45045</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+6792</t>
+          <t>+6960</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -68,6 +68,7 @@
     <sheet name="2026-09-11" sheetId="59" state="visible" r:id="rId59"/>
     <sheet name="2026-09-12" sheetId="60" state="visible" r:id="rId60"/>
     <sheet name="2026-09-13" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="2026-09-14" sheetId="62" state="visible" r:id="rId62"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51475,6 +51476,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-14 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>6672</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2975</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>23216</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+5712</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ZÎ£ WHITÎ£BÎ£ARD</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+476</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>AangEX2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>5520</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>8409</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>SeeYuSoon</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2184</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>6474</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>35558</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>21360</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>32941</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | $ignature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>5074</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>16002</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>7162</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>52941</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+7896</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>43140</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+8217</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>10283</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1084</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -51500,7 +51500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-14 13:01:00</t>
+          <t>Timestamp: 2026-09-14 13:31:00</t>
         </is>
       </c>
     </row>
@@ -52248,11 +52248,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>52941</v>
+        <v>53025</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+7896</t>
+          <t>+7980</t>
         </is>
       </c>
     </row>
@@ -52293,11 +52293,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>43140</v>
+        <v>43224</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+8217</t>
+          <t>+8301</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -69,6 +69,7 @@
     <sheet name="2026-09-12" sheetId="60" state="visible" r:id="rId60"/>
     <sheet name="2026-09-13" sheetId="61" state="visible" r:id="rId61"/>
     <sheet name="2026-09-14" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="2026-09-15" sheetId="63" state="visible" r:id="rId63"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -52355,6 +52356,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-15 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>6672</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>206</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2975</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>24980</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1764</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>ZÎ£ WHITÎ£BÎ£ARD</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>AangEX2</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>5520</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>8409</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>SeeYuSoon</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2198</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>6894</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1443</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>35978</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>21360</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>33361</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | $ignature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+318</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>5494</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>16002</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>321</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+321</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>7162</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>56973</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+3948</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>46131</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2907</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>10283</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1504</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -52380,7 +52380,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-15 13:01:00</t>
+          <t>Timestamp: 2026-09-15 13:31:00</t>
         </is>
       </c>
     </row>
@@ -52498,11 +52498,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>24980</v>
+        <v>25064</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+1764</t>
+          <t>+1848</t>
         </is>
       </c>
     </row>
@@ -53128,11 +53128,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>56973</v>
+        <v>57057</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+3948</t>
+          <t>+4032</t>
         </is>
       </c>
     </row>
@@ -53173,11 +53173,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>46131</v>
+        <v>46215</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+2907</t>
+          <t>+2991</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -70,6 +70,7 @@
     <sheet name="2026-09-13" sheetId="61" state="visible" r:id="rId61"/>
     <sheet name="2026-09-14" sheetId="62" state="visible" r:id="rId62"/>
     <sheet name="2026-09-15" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="2026-09-16" sheetId="64" state="visible" r:id="rId64"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53235,6 +53236,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-16 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>f0rgotten</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>805</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4984</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>26828</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1764</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ZÎ£ WHITÎ£BÎ£ARD</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>AangEX2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>7122</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+1602</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>8409</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>SeeYouSoon</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2254</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>416</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+366</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6894</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1443</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>35978</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>21360</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>33361</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | $ignature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>5494</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2048</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+368</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>16002</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>321</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>7162</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>60719</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3662</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>3030</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>48443</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2228</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>10283</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1504</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -53260,7 +53260,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-16 13:01:00</t>
+          <t>Timestamp: 2026-09-16 13:31:00</t>
         </is>
       </c>
     </row>
@@ -53348,11 +53348,11 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4984</v>
+        <v>5068</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>+2009</t>
+          <t>+2093</t>
         </is>
       </c>
     </row>
@@ -53438,11 +53438,11 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>7122</v>
+        <v>7206</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>+1602</t>
+          <t>+1686</t>
         </is>
       </c>
     </row>
@@ -53993,11 +53993,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>60719</v>
+        <v>60725</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3662</t>
+          <t>+3668</t>
         </is>
       </c>
     </row>
@@ -54038,7 +54038,7 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>3030</v>
+        <v>3114</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -71,6 +71,7 @@
     <sheet name="2026-09-14" sheetId="62" state="visible" r:id="rId62"/>
     <sheet name="2026-09-15" sheetId="63" state="visible" r:id="rId63"/>
     <sheet name="2026-09-16" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="2026-09-17" sheetId="65" state="visible" r:id="rId65"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54115,6 +54116,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-17 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>f0rgotten</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>805</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6637</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+1569</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>28430</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1602</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ZÎ£ WHITÎ£BÎ£ARD</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>AangEX2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>8814</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+1608</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>8409</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>SeeYouSoon</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2254</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>836</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>C.L.A.Z</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>8467</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+1573</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+477</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>36398</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>21360</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>33781</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | $ignature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SESSHOMARU</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>6729</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1235</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2048</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>16002</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>321</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>7162</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>64478</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3753</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>6750</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+3636</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>51497</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3054</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>10283</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1504</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -54140,7 +54140,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-17 13:01:00</t>
+          <t>Timestamp: 2026-09-17 13:31:00</t>
         </is>
       </c>
     </row>
@@ -54498,11 +54498,11 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>8467</v>
+        <v>8499</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>+1573</t>
+          <t>+1605</t>
         </is>
       </c>
     </row>
@@ -54873,11 +54873,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>64478</v>
+        <v>64562</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3753</t>
+          <t>+3837</t>
         </is>
       </c>
     </row>
@@ -54918,11 +54918,11 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>6750</v>
+        <v>6866</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>+3636</t>
+          <t>+3752</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -72,6 +72,7 @@
     <sheet name="2026-09-15" sheetId="63" state="visible" r:id="rId63"/>
     <sheet name="2026-09-16" sheetId="64" state="visible" r:id="rId64"/>
     <sheet name="2026-09-17" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="2026-09-18" sheetId="66" state="visible" r:id="rId66"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54995,6 +54996,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-18 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>f0rgotten</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>805</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>865</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+645</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>9454</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+2817</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>30032</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1602</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ZÎ£ WHITÎ£BÎ£ARD</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>AangEX2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>8814</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>851</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+851</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>8409</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>SeeYouSoon</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2254</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>836</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>C.L.A.Z</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>8885</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+386</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>36818</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>21360</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>675</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+675</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>34201</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | $ignature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SESSHOMARU</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>6940</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+211</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2048</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>16002</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>321</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>7164</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>68250</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3688</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>8157</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1291</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>54261</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2764</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>10283</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1504</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -55020,7 +55020,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-18 13:01:00</t>
+          <t>Timestamp: 2026-09-18 13:31:00</t>
         </is>
       </c>
     </row>
@@ -55753,11 +55753,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>68250</v>
+        <v>68334</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3688</t>
+          <t>+3772</t>
         </is>
       </c>
     </row>
@@ -55813,11 +55813,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>54261</v>
+        <v>54332</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+2764</t>
+          <t>+2835</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -73,6 +73,7 @@
     <sheet name="2026-09-16" sheetId="64" state="visible" r:id="rId64"/>
     <sheet name="2026-09-17" sheetId="65" state="visible" r:id="rId65"/>
     <sheet name="2026-09-18" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="2026-09-19" sheetId="67" state="visible" r:id="rId67"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55875,6 +55876,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-19 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>f0rgotten</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>805</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>866</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>9454</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>31544</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1512</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ZÎ£ WHITÎ£BÎ£ARD</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>476</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>AangEX2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>8814</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>851</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>8409</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>SeeYouSoon</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>2268</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>836</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>C.L.A.Z</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>8885</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2340</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>37238</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>21360</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>675</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>34621</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | $ignature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>SESSHOMARU</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>6940</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2048</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>16002</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Mode pilot</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>321</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>7164</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>72269</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3935</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>9630</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1473</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>57637</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3305</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>10283</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+504</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -55900,7 +55900,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-19 13:01:00</t>
+          <t>Timestamp: 2026-09-19 13:31:00</t>
         </is>
       </c>
     </row>
@@ -56198,11 +56198,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>2268</v>
+        <v>2352</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+14</t>
+          <t>+98</t>
         </is>
       </c>
     </row>
@@ -56633,11 +56633,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>72269</v>
+        <v>72383</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3935</t>
+          <t>+4049</t>
         </is>
       </c>
     </row>
@@ -56678,11 +56678,11 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>9630</v>
+        <v>9667</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>+1473</t>
+          <t>+1510</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -74,6 +74,7 @@
     <sheet name="2026-09-17" sheetId="65" state="visible" r:id="rId65"/>
     <sheet name="2026-09-18" sheetId="66" state="visible" r:id="rId66"/>
     <sheet name="2026-09-19" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="2026-09-20" sheetId="68" state="visible" r:id="rId68"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -56755,6 +56756,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-20 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>21241</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+21241</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>f0rgotten</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20875</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+20070</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>17641</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+17641</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>23444</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+22578</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>33144</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+23690</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>54603</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+23059</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>21731</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+21731</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>20480</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+19660</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ZÎ£ WHITÎ£BÎ£ARD</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20302</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+19826</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>27235</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+27235</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>AangEX2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>29760</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+20946</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>22165</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+22165</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>21043</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+20192</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>21770</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+21770</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>22106</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+21082</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>20151</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>28768</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+20359</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>19887</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+19887</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>SeeYouSoon</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>25992</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+23640</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>21235</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+20399</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>10610</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+10610</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>C.L.A.Z</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>22101</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+22101</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>29102</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+20217</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>24795</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+22455</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>20393</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+20393</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>118297</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+118297</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>63791</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+26553</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>42409</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+21049</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>112630</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+112630</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Me®u</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>28272</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>57750</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+23129</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | $ignature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>10178</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+10178</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>9199</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+9199</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshõmaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>21998</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>19193</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+19144</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>21763</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+21763</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>22323</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+22005</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>29020</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+22080</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>18708</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+18708</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>22814</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+20766</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>19852</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+19852</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>21772</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+21772</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>21521</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+21507</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>39891</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+23889</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>26527</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+21999</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>20614</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>27357</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+20193</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>98821</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+26438</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>22153</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+21481</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>21244</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+21216</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>RS | Oboy Max</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>35255</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+25588</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>83918</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+26281</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>20947</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+20947</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>30054</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+19771</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>22085</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+20077</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -56780,7 +56780,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-20 13:01:00</t>
+          <t>Timestamp: 2026-09-20 13:31:00</t>
         </is>
       </c>
     </row>
@@ -57074,7 +57074,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>SeeYouSoon</t>
+          <t>SNC | Asuna</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
@@ -57082,7 +57082,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+23640</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
